--- a/fixtures/power-query-remove-duplicates_fixture.xlsx
+++ b/fixtures/power-query-remove-duplicates_fixture.xlsx
@@ -752,9 +752,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4">
+      <c r="A4" t="str">
         <f>""</f>
-        <v/>
       </c>
       <c r="B4" t="n">
         <v>888</v>

--- a/fixtures/power-query-remove-duplicates_fixture.xlsx
+++ b/fixtures/power-query-remove-duplicates_fixture.xlsx
@@ -15,7 +15,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case6_Source" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="Case1Source">'Case1_Source'!$A$1:$B$4</definedName>
+    <definedName name="Case2Source">'Case2_Source'!$A$1:$C$4</definedName>
+    <definedName name="Case3Source">'Case3_Source'!$A$1:$C$4</definedName>
+    <definedName name="Case4Source">'Case4_Source'!$A$1:$B$5</definedName>
+    <definedName name="Case5Source">'Case5_Source'!$A$1:$D$4</definedName>
+    <definedName name="Case6Source">'Case6_Source'!$A$1:$D$3</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -135,78 +142,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Case1Source" displayName="Case1Source" ref="A1:B4" headerRowCount="1">
-  <autoFilter ref="A1:B4"/>
-  <tableColumns count="2">
-    <tableColumn id="1" name="CustomerID"/>
-    <tableColumn id="2" name="Amount"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Case2Source" displayName="Case2Source" ref="A1:C4" headerRowCount="1">
-  <autoFilter ref="A1:C4"/>
-  <tableColumns count="3">
-    <tableColumn id="1" name="CustomerID"/>
-    <tableColumn id="2" name="UpdatedDate"/>
-    <tableColumn id="3" name="Amount"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</table>
-</file>
-
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Case3Source" displayName="Case3Source" ref="A1:C4" headerRowCount="1">
-  <autoFilter ref="A1:C4"/>
-  <tableColumns count="3">
-    <tableColumn id="1" name="CustomerID"/>
-    <tableColumn id="2" name="OrderDate"/>
-    <tableColumn id="3" name="Amount"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</table>
-</file>
-
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Case4Source" displayName="Case4Source" ref="A1:B5" headerRowCount="1">
-  <autoFilter ref="A1:B5"/>
-  <tableColumns count="2">
-    <tableColumn id="1" name="CustomerID"/>
-    <tableColumn id="2" name="Amount"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</table>
-</file>
-
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Case5Source" displayName="Case5Source" ref="A1:D4" headerRowCount="1">
-  <autoFilter ref="A1:D4"/>
-  <tableColumns count="4">
-    <tableColumn id="1" name="CustomerID"/>
-    <tableColumn id="2" name="UpdatedDate"/>
-    <tableColumn id="3" name="RowID"/>
-    <tableColumn id="4" name="Amount"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</table>
-</file>
-
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Case6Source" displayName="Case6Source" ref="A1:D3" headerRowCount="1">
-  <autoFilter ref="A1:D3"/>
-  <tableColumns count="4">
-    <tableColumn id="1" name="CustomerID"/>
-    <tableColumn id="2" name="OrderDate"/>
-    <tableColumn id="3" name="RowID"/>
-    <tableColumn id="4" name="Amount"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -549,9 +484,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -627,9 +559,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -705,9 +634,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -771,9 +697,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -864,9 +787,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -938,9 +858,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -950,7 +867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A113"/>
+  <dimension ref="A1:A123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -959,7 +876,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Fixture for Pilot A — power-query-remove-duplicates</t>
+          <t>Fixture for Pilot A - power-query-remove-duplicates</t>
         </is>
       </c>
     </row>
@@ -969,731 +886,801 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>This fixture has one source Excel Table per case (Case1Source..Case6Source), on their own</t>
+          <t>This fixture has one source sheet per case, with the data range registered as a workbook-level</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>sheets. openpyxl cannot create actual Power Query queries (Power Query isn't a cell-formula</t>
+          <t>Named Range (Case1Source..Case6Source) rather than an Excel Table, so Power Query can find it</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>feature), so for each case you build one Power Query query yourself: Data &gt; Get &amp; Transform</t>
+          <t>via Excel.CurrentWorkbook(). For each case: Data &gt; Get &amp; Transform &gt; From Table/Range is not</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>&gt; From Table/Range on that case's source table, then Home &gt; Advanced Editor in the Power</t>
+          <t>used here since there's no Table object - instead, go to Data &gt; Get Data &gt; From Other Sources &gt;</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Query Editor, select all, and paste the M code below in place of the default. Close &amp; Load</t>
+          <t>Blank Query, then Home &gt; Advanced Editor, select all, and paste the M code below (it already</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>to a new sheet, then screenshot per the plan at the bottom.</t>
+          <t>starts from Excel.CurrentWorkbook() and picks up the case's named range directly - no manual</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>range selection needed). Because named ranges are not table objects, the first M step after</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <f>== Case 1 — Basic duplicate key ===</f>
-        <v/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Source promotes the first row to column headers (Table.PromoteHeaders) - this replaces the</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Source table: Case1Source</t>
+          <t>automatic header-row detection you'd otherwise get for free from a real Excel Table. Close &amp;</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M code:</t>
+          <t>Load, then screenshot per the plan at the bottom.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>let</t>
-        </is>
-      </c>
+      <c r="A13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Source = Excel.CurrentWorkbook(){[Name="Case1Source"]}[Content],</t>
-        </is>
+      <c r="A14">
+        <f>== Case 1 - Basic duplicate key ===</f>
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Grouped = Table.Group(Source, {"CustomerID"}, {{"Chosen", each Table.First(_), type record}}),</t>
+          <t>Source named range: Case1Source</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Expanded = Table.ExpandRecordColumn(Grouped, "Chosen", List.Difference(Table.ColumnNames(Source), {"CustomerID"}))</t>
+          <t>M code:</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>in</t>
+          <t>let</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Expanded</t>
+          <t xml:space="preserve">    RawSource = Excel.CurrentWorkbook(){[Name="Case1Source"]}[Content],</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Expected result: 2 rows — one per CustomerID (C1, C2). Which C1 row survives is not</t>
+          <t xml:space="preserve">    Source = Table.PromoteHeaders(RawSource, [PromoteAllScalars=true]),</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>guaranteed by this case (no sort), so either Amount 100 or 150 for C1 is correct.</t>
+          <t xml:space="preserve">    Grouped = Table.Group(Source, {"CustomerID"}, {{"Chosen", each Table.First(_), type record}}),</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Expanded = Table.ExpandRecordColumn(Grouped, "Chosen", List.Difference(Table.ColumnNames(Source), {"CustomerID"}))</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <f>== Case 2 — Keep latest row per ID ===</f>
-        <v/>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Source table: Case2Source</t>
+          <t xml:space="preserve">    Expanded</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M code:</t>
+          <t>Expected result: 2 rows - one per CustomerID (C1, C2). Which C1 row survives is not</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>let</t>
+          <t>guaranteed by this case (no sort), so either Amount 100 or 150 for C1 is correct.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Source = Excel.CurrentWorkbook(){[Name="Case2Source"]}[Content],</t>
-        </is>
-      </c>
+      <c r="A26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Grouped = Table.Group(Source, {"CustomerID"}, {{"Chosen", each Table.First(Table.Sort(_, {{"UpdatedDate", Order.Descending}})), type record}}),</t>
-        </is>
+      <c r="A27">
+        <f>== Case 2 - Keep latest row per ID ===</f>
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Expanded = Table.ExpandRecordColumn(Grouped, "Chosen", List.Difference(Table.ColumnNames(Source), {"CustomerID"}))</t>
+          <t>Source named range: Case2Source</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>in</t>
+          <t>M code:</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Expanded</t>
+          <t>let</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Expected result: C1 row with UpdatedDate 2024-01-15 / Amount 120 (the older 2024-01-10 row</t>
+          <t xml:space="preserve">    RawSource = Excel.CurrentWorkbook(){[Name="Case2Source"]}[Content],</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>is dropped); C2 row with Amount 200 unchanged.</t>
+          <t xml:space="preserve">    Source = Table.PromoteHeaders(RawSource, [PromoteAllScalars=true]),</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Grouped = Table.Group(Source, {"CustomerID"}, {{"Chosen", each Table.First(Table.Sort(_, {{"UpdatedDate", Order.Descending}})), type record}}),</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <f>== Case 3 — Two-column composite key ===</f>
-        <v/>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Expanded = Table.ExpandRecordColumn(Grouped, "Chosen", List.Difference(Table.ColumnNames(Source), {"CustomerID"}))</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Source table: Case3Source</t>
+          <t>in</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>M code:</t>
+          <t xml:space="preserve">    Expanded</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>let</t>
+          <t>Expected result: C1 row with UpdatedDate 2024-01-15 / Amount 120 (the older 2024-01-10 row</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Source = Excel.CurrentWorkbook(){[Name="Case3Source"]}[Content],</t>
+          <t>is dropped); C2 row with Amount 200 unchanged.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Grouped = Table.Group(Source, {"CustomerID", "OrderDate"}, {{"Chosen", each Table.First(_), type record}}),</t>
-        </is>
-      </c>
+      <c r="A39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Expanded = Table.ExpandRecordColumn(Grouped, "Chosen", List.Difference(Table.ColumnNames(Source), {"CustomerID", "OrderDate"}))</t>
-        </is>
+      <c r="A40">
+        <f>== Case 3 - Two-column composite key ===</f>
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>in</t>
+          <t>Source named range: Case3Source</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Expanded</t>
+          <t>M code:</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Expected result: all 3 rows survive unchanged — C1/2024-01-10 and C1/2024-02-10 are</t>
+          <t>let</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>different orders from the same customer and must NOT collapse into one row. This is the</t>
+          <t xml:space="preserve">    RawSource = Excel.CurrentWorkbook(){[Name="Case3Source"]}[Content],</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>screenshot that demonstrates the difference from Case 1/2 (which group on CustomerID alone).</t>
+          <t xml:space="preserve">    Source = Table.PromoteHeaders(RawSource, [PromoteAllScalars=true]),</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr"/>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Grouped = Table.Group(Source, {"CustomerID", "OrderDate"}, {{"Chosen", each Table.First(_), type record}}),</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <f>== Case 4 — Blank or null keys ===</f>
-        <v/>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Expanded = Table.ExpandRecordColumn(Grouped, "Chosen", List.Difference(Table.ColumnNames(Source), {"CustomerID", "OrderDate"}))</t>
+        </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Source table: Case4Source</t>
+          <t>in</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Note: row 2's CustomerID is a true blank/null cell (nothing entered). Row 3's CustomerID</t>
+          <t xml:space="preserve">    Expanded</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>is the formula ="" so the cell evaluates to a genuine zero-length TEXT value, not a</t>
+          <t>Expected result: all 3 rows survive unchanged - C1/2024-01-10 and C1/2024-02-10 are</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>blank - this is how a real empty string usually reaches Excel (a formula, an import, or a</t>
+          <t>different orders from the same customer and must NOT collapse into one row. This is the</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>linked source), since typing into a cell and clearing it always leaves a true blank/null.</t>
+          <t>screenshot that demonstrates the difference from Case 1/2 (which group on CustomerID alone).</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>These are deliberately different so the query can be seen NOT collapsing them together.</t>
-        </is>
-      </c>
+      <c r="A53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>M code:</t>
-        </is>
+      <c r="A54">
+        <f>== Case 4 - Blank or null keys ===</f>
+        <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>let</t>
+          <t>Source named range: Case4Source</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Source = Excel.CurrentWorkbook(){[Name="Case4Source"]}[Content],</t>
+          <t>Note: row 2's CustomerID is a true blank/null cell (nothing entered). Row 3's CustomerID</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">    HasID = Table.SelectRows(Source, each [CustomerID] &lt;&gt; null and [CustomerID] &lt;&gt; ""),</t>
+          <t>is the formula ="" so the cell evaluates to a genuine zero-length TEXT value, not a</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">    NoID = Table.SelectRows(Source, each [CustomerID] = null or [CustomerID] = ""),</t>
+          <t>blank - this is how a real empty string usually reaches Excel (a formula, an import, or a</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">    GroupedHasID = Table.Group(HasID, {"CustomerID"}, {{"Chosen", each Table.First(_), type record}}),</t>
+          <t>linked source), since typing into a cell and clearing it always leaves a true blank/null.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ExpandedHasID = Table.ExpandRecordColumn(GroupedHasID, "Chosen", List.Difference(Table.ColumnNames(HasID), {"CustomerID"})),</t>
+          <t>These are deliberately different so the query can be seen NOT collapsing them together.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Combined = Table.Combine({ExpandedHasID, NoID})</t>
+          <t>M code:</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>in</t>
+          <t>let</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Combined</t>
+          <t xml:space="preserve">    RawSource = Excel.CurrentWorkbook(){[Name="Case4Source"]}[Content],</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Expected result: 4 rows total — C1/100, C2/200 (deduped side, no actual duplicates here so</t>
+          <t xml:space="preserve">    Source = Table.PromoteHeaders(RawSource, [PromoteAllScalars=true]),</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>both pass through), plus BOTH blank-key rows (Amount 999 and 888) preserved separately, not</t>
+          <t xml:space="preserve">    HasID = Table.SelectRows(Source, each [CustomerID] &lt;&gt; null and [CustomerID] &lt;&gt; ""),</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>collapsed into a single blank-key row. This is the key thing to screenshot: two blank-key rows,</t>
+          <t xml:space="preserve">    NoID = Table.SelectRows(Source, each [CustomerID] = null or [CustomerID] = ""),</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>not one.</t>
+          <t xml:space="preserve">    GroupedHasID = Table.Group(HasID, {"CustomerID"}, {{"Chosen", each Table.First(_), type record}}),</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr"/>
+      <c r="A68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ExpandedHasID = Table.ExpandRecordColumn(GroupedHasID, "Chosen", List.Difference(Table.ColumnNames(HasID), {"CustomerID"})),</t>
+        </is>
+      </c>
     </row>
     <row r="69">
-      <c r="A69">
-        <f>== Case 5 — Same-date tie ===</f>
-        <v/>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Combined = Table.Combine({ExpandedHasID, NoID})</t>
+        </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Source table: Case5Source</t>
+          <t>in</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>M code:</t>
+          <t xml:space="preserve">    Combined</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>let</t>
+          <t>Expected result: 4 rows total - C1/100, C2/200 (deduped side, no actual duplicates here so</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Source = Excel.CurrentWorkbook(){[Name="Case5Source"]}[Content],</t>
+          <t>both pass through), plus BOTH blank-key rows (Amount 999 and 888) preserved separately, not</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Grouped = Table.Group(Source, {"CustomerID"}, {{"Chosen", each Table.First(Table.Sort(_, {{"UpdatedDate", Order.Descending}, {"RowID", Order.Descending}})), type record}}),</t>
+          <t>collapsed into a single blank-key row. This is the key thing to screenshot: two blank-key rows,</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Expanded = Table.ExpandRecordColumn(Grouped, "Chosen", List.Difference(Table.ColumnNames(Source), {"CustomerID"}))</t>
+          <t>not one.</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>in</t>
-        </is>
-      </c>
+      <c r="A76" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Expanded</t>
-        </is>
+      <c r="A77">
+        <f>== Case 5 - Same-date tie ===</f>
+        <v/>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Expected result: 1 row for C1 — UpdatedDate 2024-01-15, RowID 3, Amount 160 (RowID 2 also</t>
+          <t>Source named range: Case5Source</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>has UpdatedDate 2024-01-15, tied; RowID descending picks RowID 3 as the deterministic winner).</t>
+          <t>M code:</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr"/>
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>let</t>
+        </is>
+      </c>
     </row>
     <row r="81">
-      <c r="A81">
-        <f>== Case 6 — Null dates (combined with RowID tiebreak) ===</f>
-        <v/>
+      <c r="A81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    RawSource = Excel.CurrentWorkbook(){[Name="Case5Source"]}[Content],</t>
+        </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Source table: Case6Source</t>
+          <t xml:space="preserve">    Source = Table.PromoteHeaders(RawSource, [PromoteAllScalars=true]),</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>M code:</t>
+          <t xml:space="preserve">    Grouped = Table.Group(Source, {"CustomerID"}, {{"Chosen", each Table.First(Table.Sort(_, {{"UpdatedDate", Order.Descending}, {"RowID", Order.Descending}})), type record}}),</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>let</t>
+          <t xml:space="preserve">    Expanded = Table.ExpandRecordColumn(Grouped, "Chosen", List.Difference(Table.ColumnNames(Source), {"CustomerID"}))</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Source = Excel.CurrentWorkbook(){[Name="Case6Source"]}[Content],</t>
+          <t>in</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WithSortDate = Table.AddColumn(Source, "_SortDate", each if [OrderDate] = null then #date(1900,1,1) else [OrderDate]),</t>
+          <t xml:space="preserve">    Expanded</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Grouped = Table.Group(WithSortDate, {"CustomerID"}, {{"Chosen", each Table.First(Table.Sort(_, {{"_SortDate", Order.Descending}, {"RowID", Order.Descending}})), type record}}),</t>
+          <t>Expected result: 1 row for C1 - UpdatedDate 2024-01-15, RowID 3, Amount 160 (RowID 2 also</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Expanded = Table.ExpandRecordColumn(Grouped, "Chosen", List.Difference(Table.ColumnNames(WithSortDate), {"CustomerID"}))</t>
+          <t>has UpdatedDate 2024-01-15, tied; RowID descending picks RowID 3 as the deterministic winner).</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>in</t>
-        </is>
-      </c>
+      <c r="A89" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Expanded</t>
-        </is>
+      <c r="A90">
+        <f>== Case 6 - Null dates (combined with RowID tiebreak) ===</f>
+        <v/>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Expected result: 1 row for C1 — RowID 2, OrderDate 2024-02-01, Amount 150. RowID 1 (null</t>
+          <t>Source named range: Case6Source</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>OrderDate, substituted to 1900-01-01) correctly loses to the real, later date.</t>
+          <t>M code:</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr"/>
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>let</t>
+        </is>
+      </c>
     </row>
     <row r="94">
-      <c r="A94">
-        <f>== Case 7 — Query folding (no new data; reuse Case 1's query) ===</f>
-        <v/>
+      <c r="A94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    RawSource = Excel.CurrentWorkbook(){[Name="Case6Source"]}[Content],</t>
+        </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Open Case 1's query in the Power Query Editor, right-click the last step, or check the query's</t>
+          <t xml:space="preserve">    Source = Table.PromoteHeaders(RawSource, [PromoteAllScalars=true]),</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>context menu / the ribbon's 'View Native Query' option.</t>
+          <t xml:space="preserve">    WithSortDate = Table.AddColumn(Source, "_SortDate", each if [OrderDate] = null then #date(1900,1,1) else [OrderDate]),</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Expected: 'View Native Query' is greyed out / unavailable, because the source is</t>
+          <t xml:space="preserve">    Grouped = Table.Group(WithSortDate, {"CustomerID"}, {{"Chosen", each Table.First(Table.Sort(_, {{"_SortDate", Order.Descending}, {"RowID", Order.Descending}})), type record}}),</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Excel.CurrentWorkbook() (an in-workbook table), not a foldable external source like a database.</t>
+          <t xml:space="preserve">    Expanded = Table.ExpandRecordColumn(Grouped, "Chosen", List.Difference(Table.ColumnNames(WithSortDate), {"CustomerID"}))</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr"/>
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
     </row>
     <row r="100">
-      <c r="A100">
-        <f>== Case 8 — Deterministic result (reuse Case 6's query) ===</f>
-        <v/>
+      <c r="A100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Expanded</t>
+        </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Right-click Case 6's query result table (or its query in the Queries pane) and choose Refresh.</t>
+          <t>Expected result: 1 row for C1 - RowID 2, OrderDate 2024-02-01, Amount 150. RowID 1 (null</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Expected: the exact same single row (RowID 2, Amount 150) as before the refresh — same input,</t>
+          <t>OrderDate, substituted to 1900-01-01) correctly loses to the real, later date.</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>same output every time, no dependence on row order or a silent tie-break.</t>
-        </is>
-      </c>
+      <c r="A103" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr"/>
+      <c r="A104">
+        <f>== Case 7 - Query folding (no new data; reuse Case 1's query) ===</f>
+        <v/>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Screenshot plan (8 screenshots, matching QA package section 4):</t>
+          <t>Open Case 1's query in the Power Query Editor, right-click the last step, or check the query's</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1) Case 1 result table -&gt; alt: 'Power Query grouped table showing one row kept per duplicate key'</t>
+          <t>context menu / the ribbon's 'View Native Query' option.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2) Case 2 result table -&gt; alt: 'Power Query result keeping only the most recently updated row per customer ID'</t>
+          <t>Expected: 'View Native Query' is greyed out / unavailable, because the source is</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>3) Case 3 result table (all 3 rows) -&gt; alt: 'Power Query grouping on a two-column composite key preserving distinct combinations'</t>
+          <t>Excel.CurrentWorkbook() (an in-workbook named range), not a foldable external source like a database.</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>4) Case 4 result table (4 rows, 2 blank-key) -&gt; alt: 'Power Query table with blank-key rows routed around the deduplication step'</t>
-        </is>
-      </c>
+      <c r="A109" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>5) Case 5 result table (RowID 3 / Amount 160) -&gt; alt: 'Power Query same-date tie broken by a secondary RowID sort'</t>
-        </is>
+      <c r="A110">
+        <f>== Case 8 - Deterministic result (reuse Case 6's query) ===</f>
+        <v/>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>6) Case 6's WithSortDate step (showing the _SortDate column and its substituted value) -&gt; alt: 'Power Query helper column substituting a placeholder date for null dates before sorting'</t>
+          <t>Right-click Case 6's query result table (or its query in the Queries pane) and choose Refresh.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>7) Case 7's greyed-out 'View Native Query' -&gt; alt: 'Power Query showing query folding is not applicable for an Excel.CurrentWorkbook source'</t>
+          <t>Expected: the exact same single row (RowID 2, Amount 150) as before the refresh - same input,</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
+        <is>
+          <t>same output every time, no dependence on row order or a silent tie-break.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Screenshot plan (8 screenshots, matching QA package section 4):</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>1) Case 1 result table -&gt; alt: 'Power Query grouped table showing one row kept per duplicate key'</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2) Case 2 result table -&gt; alt: 'Power Query result keeping only the most recently updated row per customer ID'</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>3) Case 3 result table (all 3 rows) -&gt; alt: 'Power Query grouping on a two-column composite key preserving distinct combinations'</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>4) Case 4 result table (4 rows, 2 blank-key) -&gt; alt: 'Power Query table with blank-key rows routed around the deduplication step'</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>5) Case 5 result table (RowID 3 / Amount 160) -&gt; alt: 'Power Query same-date tie broken by a secondary RowID sort'</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>6) Case 6's WithSortDate step (showing the _SortDate column and its substituted value) -&gt; alt: 'Power Query helper column substituting a placeholder date for null dates before sorting'</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>7) Case 7's greyed-out 'View Native Query' -&gt; alt: 'Power Query showing query folding is not applicable for an Excel.CurrentWorkbook source'</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
         <is>
           <t>8) Case 8's result after Refresh, unchanged -&gt; alt: 'Power Query deduplication result unchanged after refresh, confirming deterministic output'</t>
         </is>

--- a/fixtures/power-query-remove-duplicates_fixture.xlsx
+++ b/fixtures/power-query-remove-duplicates_fixture.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="71">
   <si>
     <t xml:space="preserve">CustomerID</t>
   </si>
@@ -66,28 +66,28 @@
     <t xml:space="preserve">Named Range (Case1Source..Case6Source) rather than an Excel Table, so Power Query can find it</t>
   </si>
   <si>
-    <t xml:space="preserve">via Excel.CurrentWorkbook(). For each case: Data &gt; Get &amp; Transform &gt; From Table/Range is not</t>
-  </si>
-  <si>
-    <t xml:space="preserve">used here since there's no Table object - instead, go to Data &gt; Get Data &gt; From Other Sources &gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blank Query, then Home &gt; Advanced Editor, select all, and paste the M code below (it already</t>
-  </si>
-  <si>
-    <t xml:space="preserve">starts from Excel.CurrentWorkbook() and picks up the case's named range directly - no manual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">range selection needed). Because named ranges are not table objects, the first M step after</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Source promotes the first row to column headers (Table.PromoteHeaders) - this replaces the</t>
-  </si>
-  <si>
-    <t xml:space="preserve">automatic header-row detection you'd otherwise get for free from a real Excel Table. Close &amp;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Load, then screenshot per the plan at the bottom.</t>
+    <t xml:space="preserve">via Excel.CurrentWorkbook(). For each case: go to Data &gt; Get Data &gt; From Other Sources &gt; Blank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Query, then Home &gt; Advanced Editor, select all, and paste the M code below (it already starts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">from Excel.CurrentWorkbook() and picks up the case's named range directly). Because named</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ranges are not table objects, the first M step after Source promotes the first row to column</t>
+  </si>
+  <si>
+    <t xml:space="preserve">headers (Table.PromoteHeaders) - this replaces the automatic header-row detection you'd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">otherwise get for free from a real Excel Table. Close &amp; Load, then screenshot per the plan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">at the bottom.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-- Case 1 - Basic duplicate key --</t>
   </si>
   <si>
     <t xml:space="preserve">Source named range: Case1Source</t>
@@ -117,10 +117,10 @@
     <t xml:space="preserve">    Expanded</t>
   </si>
   <si>
-    <t xml:space="preserve">Expected result: 2 rows - one per CustomerID (C1, C2). Which C1 row survives is not</t>
-  </si>
-  <si>
-    <t xml:space="preserve">guaranteed by this case (no sort), so either Amount 100 or 150 for C1 is correct.</t>
+    <t xml:space="preserve">Expected result: 2 rows - one per CustomerID (C1, C2). Either Amount 100 or 150 for C1 is correct.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-- Case 2 - Keep latest row per ID --</t>
   </si>
   <si>
     <t xml:space="preserve">Source named range: Case2Source</t>
@@ -132,10 +132,10 @@
     <t xml:space="preserve">    Grouped = Table.Group(Source, {"CustomerID"}, {{"Chosen", each Table.First(Table.Sort(_, {{"UpdatedDate", Order.Descending}})), type record}}),</t>
   </si>
   <si>
-    <t xml:space="preserve">Expected result: C1 row with UpdatedDate 2024-01-15 / Amount 120 (the older 2024-01-10 row</t>
-  </si>
-  <si>
-    <t xml:space="preserve">is dropped); C2 row with Amount 200 unchanged.</t>
+    <t xml:space="preserve">Expected result: C1 -&gt; UpdatedDate 2024-01-15 / Amount 120. C2 -&gt; 200 unchanged.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-- Case 3 - Two-column composite key --</t>
   </si>
   <si>
     <t xml:space="preserve">Source named range: Case3Source</t>
@@ -150,31 +150,19 @@
     <t xml:space="preserve">    Expanded = Table.ExpandRecordColumn(Grouped, "Chosen", List.Difference(Table.ColumnNames(Source), {"CustomerID", "OrderDate"}))</t>
   </si>
   <si>
-    <t xml:space="preserve">Expected result: all 3 rows survive unchanged - C1/2024-01-10 and C1/2024-02-10 are</t>
-  </si>
-  <si>
-    <t xml:space="preserve">different orders from the same customer and must NOT collapse into one row. This is the</t>
-  </si>
-  <si>
-    <t xml:space="preserve">screenshot that demonstrates the difference from Case 1/2 (which group on CustomerID alone).</t>
+    <t xml:space="preserve">Expected result: all 3 rows survive unchanged.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-- Case 4 - Blank or null keys --</t>
   </si>
   <si>
     <t xml:space="preserve">Source named range: Case4Source</t>
   </si>
   <si>
-    <t xml:space="preserve">Note: row 2's CustomerID is a true blank/null cell (nothing entered). Row 3's CustomerID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">is the formula ="" so the cell evaluates to a genuine zero-length TEXT value, not a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">blank - this is how a real empty string usually reaches Excel (a formula, an import, or a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">linked source), since typing into a cell and clearing it always leaves a true blank/null.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">These are deliberately different so the query can be seen NOT collapsing them together.</t>
+    <t xml:space="preserve">Note: row 2's CustomerID is a true blank/null cell. Row 3's CustomerID is the formula ='""'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">so the cell evaluates to a genuine zero-length TEXT value, not a blank.</t>
   </si>
   <si>
     <t xml:space="preserve">    RawSource = Excel.CurrentWorkbook(){[Name="Case4Source"]}[Content],</t>
@@ -198,16 +186,10 @@
     <t xml:space="preserve">    Combined</t>
   </si>
   <si>
-    <t xml:space="preserve">Expected result: 4 rows total - C1/100, C2/200 (deduped side, no actual duplicates here so</t>
-  </si>
-  <si>
-    <t xml:space="preserve">both pass through), plus BOTH blank-key rows (Amount 999 and 888) preserved separately, not</t>
-  </si>
-  <si>
-    <t xml:space="preserve">collapsed into a single blank-key row. This is the key thing to screenshot: two blank-key rows,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">not one.</t>
+    <t xml:space="preserve">Expected result: 4 rows - C1/100, C2/200, plus BOTH blank-key rows (999, 888) kept separately.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-- Case 5 - Same-date tie --</t>
   </si>
   <si>
     <t xml:space="preserve">Source named range: Case5Source</t>
@@ -219,10 +201,10 @@
     <t xml:space="preserve">    Grouped = Table.Group(Source, {"CustomerID"}, {{"Chosen", each Table.First(Table.Sort(_, {{"UpdatedDate", Order.Descending}, {"RowID", Order.Descending}})), type record}}),</t>
   </si>
   <si>
-    <t xml:space="preserve">Expected result: 1 row for C1 - UpdatedDate 2024-01-15, RowID 3, Amount 160 (RowID 2 also</t>
-  </si>
-  <si>
-    <t xml:space="preserve">has UpdatedDate 2024-01-15, tied; RowID descending picks RowID 3 as the deterministic winner).</t>
+    <t xml:space="preserve">Expected result: 1 row for C1 - RowID 3, Amount 160.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-- Case 6 - Null dates --</t>
   </si>
   <si>
     <t xml:space="preserve">Source named range: Case6Source</t>
@@ -240,58 +222,31 @@
     <t xml:space="preserve">    Expanded = Table.ExpandRecordColumn(Grouped, "Chosen", List.Difference(Table.ColumnNames(WithSortDate), {"CustomerID"}))</t>
   </si>
   <si>
-    <t xml:space="preserve">Expected result: 1 row for C1 - RowID 2, OrderDate 2024-02-01, Amount 150. RowID 1 (null</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OrderDate, substituted to 1900-01-01) correctly loses to the real, later date.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Case 1's query in the Power Query Editor, right-click the last step, or check the query's</t>
-  </si>
-  <si>
-    <t xml:space="preserve">context menu / the ribbon's 'View Native Query' option.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Expected: 'View Native Query' is greyed out / unavailable, because the source is</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Excel.CurrentWorkbook() (an in-workbook named range), not a foldable external source like a database.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Right-click Case 6's query result table (or its query in the Queries pane) and choose Refresh.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Expected: the exact same single row (RowID 2, Amount 150) as before the refresh - same input,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">same output every time, no dependence on row order or a silent tie-break.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Screenshot plan (8 screenshots, matching QA package section 4):</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1) Case 1 result table -&gt; alt: 'Power Query grouped table showing one row kept per duplicate key'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2) Case 2 result table -&gt; alt: 'Power Query result keeping only the most recently updated row per customer ID'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3) Case 3 result table (all 3 rows) -&gt; alt: 'Power Query grouping on a two-column composite key preserving distinct combinations'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4) Case 4 result table (4 rows, 2 blank-key) -&gt; alt: 'Power Query table with blank-key rows routed around the deduplication step'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5) Case 5 result table (RowID 3 / Amount 160) -&gt; alt: 'Power Query same-date tie broken by a secondary RowID sort'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6) Case 6's WithSortDate step (showing the _SortDate column and its substituted value) -&gt; alt: 'Power Query helper column substituting a placeholder date for null dates before sorting'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7) Case 7's greyed-out 'View Native Query' -&gt; alt: 'Power Query showing query folding is not applicable for an Excel.CurrentWorkbook source'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8) Case 8's result after Refresh, unchanged -&gt; alt: 'Power Query deduplication result unchanged after refresh, confirming deterministic output'</t>
+    <t xml:space="preserve">Expected result: 1 row for C1 - RowID 2, OrderDate 2024-02-01, Amount 150.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-- Case 7 - Query folding --</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reuse Case 1's query. Check 'View Native Query' is greyed out.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-- Case 8 - Deterministic result --</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reuse Case 6's query. Refresh and confirm the same result.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Screenshot plan (8 screenshots):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1) Case 1 result / 2) Case 2 result / 3) Case 3 result (3 rows) / 4) Case 4 result (4 rows) /</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5) Case 5 result / 6) Case 6's WithSortDate step / 7) Case 7 greyed-out View Native Query /</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8) Case 8 result after Refresh</t>
   </si>
 </sst>
 </file>
@@ -965,7 +920,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A123"/>
+  <dimension ref="A1:A100"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="100"/>
@@ -1021,64 +976,58 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="e">
-        <f aca="false">= case 1 - basic duplicate key ===</f>
-        <v>#VALUE!</v>
+      <c r="A14" s="0" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1087,222 +1036,219 @@
         <v>28</v>
       </c>
     </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="s">
+        <v>29</v>
+      </c>
+    </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="e">
-        <f aca="false">= case 2 - keep latest row per id ===</f>
-        <v>#VALUE!</v>
+      <c r="A27" s="0" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="0" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="e">
-        <f aca="false">= case 3 - two-column composite key ===</f>
-        <v>#VALUE!</v>
+      <c r="A40" s="0" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="0" t="s">
-        <v>40</v>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="0" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="0" t="e">
-        <f aca="false">= case 4 - blank or null keys ===</f>
-        <v>#VALUE!</v>
+      <c r="A54" s="0" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="0" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="0" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="0" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="0" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="0" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="0" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="0" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="0" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="0" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="0" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="0" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="0" t="s">
-        <v>52</v>
+        <v>20</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="0" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="0" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1312,84 +1258,82 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="0" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="0" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="0" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="0" t="e">
-        <f aca="false">= case 5 - same-date tie ===</f>
-        <v>#VALUE!</v>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="0" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="0" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="0" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="0" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="0" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="0" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="0" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="0" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="0" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="0" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="0" t="s">
-        <v>61</v>
+        <v>25</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="0" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="0" t="s">
         <v>62</v>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="0" t="e">
-        <f aca="false">= case 6 - null dates (combined with rowid tiebreak) ===</f>
-        <v>#VALUE!</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1399,149 +1343,37 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="0" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="0" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="0" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="0" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="0" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="0" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="0" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="0" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="0" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="0" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="0" t="e">
-        <f aca="false">= case 7 - query folding (no new data; reuse case 1's query) ===)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="0" t="s">
         <v>70</v>
-      </c>
-    </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="0" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="0" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="0" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="0" t="e">
-        <f aca="false">= case 8 - deterministic result (reuse case 6's query) ===)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="0" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="0" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="0" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="0" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="0" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="0" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="0" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="0" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="0" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="0" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="0" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="0" t="s">
-        <v>85</v>
       </c>
     </row>
   </sheetData>
